--- a/sources/paul_step5b.xlsx
+++ b/sources/paul_step5b.xlsx
@@ -816,6 +816,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1bddff50-c0df-40c7-9efa-29b264583940</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>1bddff50-c0df-40c7-9efa-29b264583940</t>
@@ -853,6 +858,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>39dff7b9-ce44-4948-ad1f-b1ef695ca9a3</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>39dff7b9-ce44-4948-ad1f-b1ef695ca9a3</t>
@@ -895,6 +905,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>701e73a5-cb4f-442c-95a1-4a3d33f87d73</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>701e73a5-cb4f-442c-95a1-4a3d33f87d73</t>
@@ -937,6 +952,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0837c7ed-0764-4f99-a630-8ac829f5cd48</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>0837c7ed-0764-4f99-a630-8ac829f5cd48</t>
@@ -979,6 +999,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>8f4adaf4-8d96-4db4-9e5d-c30c5a7019be</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>8f4adaf4-8d96-4db4-9e5d-c30c5a7019be</t>
@@ -1021,6 +1046,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>9ceaa1aa-aa76-418f-a422-c4dcb6b6e146</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>9ceaa1aa-aa76-418f-a422-c4dcb6b6e146</t>
@@ -1063,6 +1093,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>b7497a64-e28b-4906-90d2-9ce8f800b5db</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>b7497a64-e28b-4906-90d2-9ce8f800b5db</t>
@@ -1115,6 +1150,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>298a11b7-cb2d-4207-89d4-785146ac1d79</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>298a11b7-cb2d-4207-89d4-785146ac1d79</t>
@@ -1162,6 +1202,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>f4807f21-048f-4fcc-be89-b4ed5bad669d</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>f4807f21-048f-4fcc-be89-b4ed5bad669d</t>
@@ -1207,6 +1252,11 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>714cac8f-98de-4f0c-bfac-510c28ebaccd</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -5170,6 +5220,11 @@
           <t>hhmmlmhmLm</t>
         </is>
       </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>8b2ab344-e968-4445-b403-e548e2f0db2d</t>
+        </is>
+      </c>
       <c r="Q92" t="inlineStr">
         <is>
           <t>8b2ab344-e968-4445-b403-e548e2f0db2d</t>
@@ -5202,6 +5257,11 @@
           <t>hhmhmhhlmm</t>
         </is>
       </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>9c058e2e-80b5-4da3-b171-a802077dec24</t>
+        </is>
+      </c>
       <c r="Q93" t="inlineStr">
         <is>
           <t>9c058e2e-80b5-4da3-b171-a802077dec24</t>
@@ -5232,6 +5292,11 @@
       <c r="K94" t="inlineStr">
         <is>
           <t>hhmmm</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>e1a2f47f-32a9-46a1-bc65-d50cded77733</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">

--- a/sources/paul_step5b.xlsx
+++ b/sources/paul_step5b.xlsx
@@ -838,6 +838,11 @@
           <t>– 1,2,1,2,1</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1,2,1,1,2</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>– Ultimate Punches</t>
@@ -883,6 +888,11 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>– 2,1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2,1,2,2,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4542,6 +4552,11 @@
       <c r="A78" t="inlineStr">
         <is>
           <t>– &lt;d+4</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>&lt;db+4</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
